--- a/testdata/configurationUAT/config_platforme.xlsx
+++ b/testdata/configurationUAT/config_platforme.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12330"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>UDID</t>
   </si>
@@ -55,39 +68,48 @@
     <t>Android</t>
   </si>
   <si>
-    <t>Pixel 4 API 30 2</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>co.infinum.nlb.uat</t>
+    <t>Pixel 4 API 35</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>rs.nlb.klik.uat</t>
+  </si>
+  <si>
+    <t>si.nlb.klik.RootActivity</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>UIAutomator2</t>
+  </si>
+  <si>
+    <t>Pixel_4</t>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
+    <t>11ffd4330fccbccbf03a55be841e04e3dc33fdbc</t>
+  </si>
+  <si>
+    <t>iOS</t>
+  </si>
+  <si>
+    <t>iPhone</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>si.nlb.klik.test</t>
   </si>
   <si>
     <t>com.backbase.model.view.activity.EnrollmentActivity</t>
   </si>
   <si>
-    <t>co.infinum.nlb.staging:id/</t>
-  </si>
-  <si>
-    <t>OFF</t>
-  </si>
-  <si>
-    <t>11ffd4330fccbccbf03a55be841e04e3dc33fdbc</t>
-  </si>
-  <si>
-    <t>iOS</t>
-  </si>
-  <si>
-    <t>iPhone</t>
-  </si>
-  <si>
-    <t>14.2</t>
-  </si>
-  <si>
-    <t>co.infinum.nlb.tst.playstore</t>
-  </si>
-  <si>
     <t>/Users/dtc/Downloads/Payload/Rzb_Release.app</t>
   </si>
   <si>
@@ -97,13 +119,10 @@
     <t>device</t>
   </si>
   <si>
-    <t>co.infinum.nlb.qa.playstore</t>
+    <t>si.nlb.klik.uat</t>
   </si>
   <si>
     <t>/Users/dtc/Downloads/dev_env-release-1.1.0.4005.3b0c377.apk</t>
-  </si>
-  <si>
-    <t>UIAutomator2</t>
   </si>
   <si>
     <t>Pixel3a</t>
@@ -112,7 +131,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -812,7 +831,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1973,7 +1992,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="26.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="50.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="22.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="21.1111111111111" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="6" max="6" width="33.2222222222222" customWidth="1"/>
+    <col min="7" max="7" width="29.8888888888889" customWidth="1"/>
+    <col min="9" max="9" width="19.7777777777778" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
@@ -2033,41 +2062,47 @@
       <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="K2" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="7"/>
+        <v>28</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="K3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2078,29 +2113,29 @@
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3">
         <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
